--- a/PFX Website.xlsx
+++ b/PFX Website.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shreyakarnik/Downloads/PFX Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D4CF7E4-6B1F-D64D-9544-7A9CFAF5FE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5855C8BA-6E57-2D4D-9B85-667EF0501DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{ABBA7690-D411-7647-80D5-984A9D0291D9}"/>
+    <workbookView xWindow="10260" yWindow="0" windowWidth="18540" windowHeight="18000" xr2:uid="{ABBA7690-D411-7647-80D5-984A9D0291D9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="FAQ" sheetId="1" r:id="rId1"/>
+    <sheet name="Proof Section PizzaForno" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,6 +37,83 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>https://www.thrillist.com/news/nation/pizzaforno-is-rolling-out-pizza-making-kiosks</t>
+  </si>
+  <si>
+    <t>Thrillist</t>
+  </si>
+  <si>
+    <t>https://curiocity.com/pizzaforno-calgary/</t>
+  </si>
+  <si>
+    <t>Curiosity</t>
+  </si>
+  <si>
+    <t>https://www.qsrmagazine.com/news/pizzaforno-sees-growth-spurt-in-first-half-of-2024/</t>
+  </si>
+  <si>
+    <t>QSR</t>
+  </si>
+  <si>
+    <t>CTV News</t>
+  </si>
+  <si>
+    <t>https://www.ctvnews.ca/kitchener/article/pizza-vending-machine-at-university-of-guelph-goes-viral-thanks-to-pizza-cam/</t>
+  </si>
+  <si>
+    <t>https://www.vendingtimes.com/news/pizza-vending-at-ontario-university-goes-viral/</t>
+  </si>
+  <si>
+    <t>Venting Times</t>
+  </si>
+  <si>
+    <t>Business Wire</t>
+  </si>
+  <si>
+    <t>https://www.businesswire.com/news/home/20250731251164/en/PizzaForno-Heats-Up-West-Coast-Expansion-with-247-Pizza-Vending-Machines-at-Southern-California-College-Campuses</t>
+  </si>
+  <si>
+    <t>Retail Insider</t>
+  </si>
+  <si>
+    <t>Fox40</t>
+  </si>
+  <si>
+    <t>https://retail-insider.com/retail-insider/2020/05/automated-pizza-oven-concept-pizzaforno-plans-to-open-thousands-of-locations/</t>
+  </si>
+  <si>
+    <t>https://fox40.com/news/local-news/sacramento-county/pizzaforno-vending-machine-california/</t>
+  </si>
+  <si>
+    <t>What is PFX?</t>
+  </si>
+  <si>
+    <t>How Do PFX Kiosks Work?</t>
+  </si>
+  <si>
+    <t>How Does PFX Ensure Pizza Quality?</t>
+  </si>
+  <si>
+    <t>How Are The Kiosks Cleaned and Maintained?</t>
+  </si>
+  <si>
+    <t>PFX or PizzaForno?</t>
+  </si>
+  <si>
+    <t>What is the ROI On These Kiosks?</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,8 +147,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,9 +486,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E25B8EC-E940-5F49-91BC-69E740595A93}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="22.6640625" defaultRowHeight="65" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="44.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="89.33203125" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="22.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6569EEED-CF05-DE49-8EAF-829816EE6756}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="27.1640625" defaultRowHeight="41" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>